--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_219_Galapagos_Isl_Ecuador.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_219_Galapagos_Isl_Ecuador.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R697d4bf3f39f4dc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rd6fd18ef396a46bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Re28e421cc445405b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R0a4c5e4416d64728"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R3f32a1e2d34c459e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R54062340fb4941a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R6c8a8f6a9dc54290"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R0c9696d505074305"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R3b91feed70bb4a61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R4bc9bd93f226433a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R505f4432ad254720"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Ra6ba0ca364614197"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ219CommercialTable" displayName="EEZ219CommercialTable" ref="A1:O7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O7"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ219CommercialTable" displayName="EEZ219CommercialTable" ref="A1:E7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E7"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ219FunctionalTable" displayName="EEZ219FunctionalTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ219FunctionalTable" displayName="EEZ219FunctionalTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ219ValidationTable" displayName="EEZ219ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ219ValidationTable" displayName="EEZ219ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -3843,7 +3797,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1108d3fc377d44ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7265470195764e8e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3853,20 +3807,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -3874,390 +3818,136 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>66.01253262990001</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>39.810717055349734</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>66.01253262990001</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>39.810717055349734</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$48,A2,'Species'!$U$2:$U$48))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>2628.006258635991</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>2.6</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>39.810717055349734</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>2628.006258635991</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>823.9610851487</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.3034688191108055</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>201.12627910850284</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>823.9610851487</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>201.71925540771318</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$48,A3,'Species'!$U$2:$U$48))</x:f>
-        <x:v>166208.81658112712</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.3034688191108055</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>201.12627910850284</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>165720.22718616232</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>488.5893949648016</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0029482785732362</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.0029482785732362245</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1979.7878426196999</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.804418819332168</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>637.4099217965255</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1979.7878426196999</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1530.321177359611</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$48,A4,'Species'!$U$2:$U$48))</x:f>
-        <x:v>3029711.2622400234</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.804418819332168</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>637.4099217965255</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1261936.413937935</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1767774.8483020884</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>2.4008430446869027</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>1.400843044686903</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>70.638199811</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.9199999999999995</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>831.76377110267</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>70.638199811</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>831.7637711026708</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$48,A5,'Species'!$U$2:$U$48))</x:f>
-        <x:v>58754.29545870134</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.9199999999999995</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>831.76377110267</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>58754.29545870128</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>5.820766091346741e-11</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0000000000000009</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>9.906962624440268e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>4428.4410175559005</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.358010718930325</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2280.398354385869</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>4428.4410175559005</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2367.4043561147873</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$48,A6,'Species'!$U$2:$U$48))</x:f>
-        <x:v>10483910.55575924</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.358010718930325</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2280.398354385869</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>10098609.608929358</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>385300.9468298815</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0381538609522238</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.03815386095222376</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>61578.9926817228</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.426028661713896</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2667.0346724275078</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>61578.9926817228</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2670.2322934822673</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$48,A7,'Species'!$U$2:$U$48))</x:f>
-        <x:v>164430214.85884443</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.426028661713896</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2667.0346724275078</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>164233308.57531446</x:v>
       </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>196906.28352996707</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0011989424388883</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.0011989424388882074</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G7">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O7">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcbe52a84cabb4a42"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbdd1230675994c3b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4267,20 +3957,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4288,606 +3968,212 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>59.05037069709999</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.58</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>3801.8939632056126</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>59.05037069709999</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>3801.8939632056126</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$48,A2,'Species'!$U$2:$U$48))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>224503.24787835806</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.58</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>3801.8939632056126</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>224503.24787835806</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>7.8515225071</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.39</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2454.7089156850284</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>7.8515225071</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2454.7089156850284</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$48,A3,'Species'!$U$2:$U$48))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>19273.20229988004</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.39</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2454.7089156850284</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>19273.20229988004</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>62147.1873478467</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.426486696072705</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2669.848979259293</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>62147.1873478467</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2671.877070987725</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$48,A4,'Species'!$U$2:$U$48))</x:f>
-        <x:v>166049644.90109006</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.426486696072705</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2669.848979259293</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>165923604.70448458</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>126040.19660547376</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0007596278831452</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0007596278831451107</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>70.638199811</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.9199999999999995</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>831.76377110267</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>70.638199811</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>831.7637711026708</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$48,A5,'Species'!$U$2:$U$48))</x:f>
-        <x:v>58754.29545870134</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.9199999999999995</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>831.76377110267</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>58754.29545870128</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>5.820766091346741e-11</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0000000000000009</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>9.906962624440268e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>4428.4410175559005</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.358010718930325</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2280.398354385869</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>4428.4410175559005</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2367.4043561147873</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$48,A6,'Species'!$U$2:$U$48))</x:f>
-        <x:v>10483910.55575924</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.358010718930325</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2280.398354385869</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>10098609.608929358</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>385300.9468298815</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0381538609522238</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.03815386095222376</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>66.01253262990001</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>39.810717055349734</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>66.01253262990001</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>39.810717055349734</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$48,A7,'Species'!$U$2:$U$48))</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>2628.006258635991</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.6</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>39.810717055349734</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
-        <x:v>2628.006258635991</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>670.0578683181</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.0937591165893554</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>124.09638104465547</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>670.0578683181</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>159.0770112205705</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$48,A8,'Species'!$U$2:$U$48))</x:f>
-        <x:v>106590.80303686995</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.0937591165893554</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>124.09638104465547</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>83151.75654877251</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>23439.046488097447</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.2818827582355319</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.2818827582355319</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>908.6085425104001</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.8091700483620397</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>644.4215399074764</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>908.6085425104001</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>970.5658869415029</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$48,A9,'Species'!$U$2:$U$48))</x:f>
-        <x:v>881864.4559442326</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.8091700483620397</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>644.4215399074764</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>585526.9161376397</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>296337.539806593</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.5061040434508957</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.5061040434508958</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>558.0325404468</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.0964245174026432</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>124.86034120850529</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>558.0325404468</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>436.5877871259103</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$48,A10,'Species'!$U$2:$U$48))</x:f>
-        <x:v>243630.19197791847</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.0964245174026432</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>124.86034120850529</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>69676.13340563647</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>173954.058572282</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>3.4966089544545524</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>2.4966089544545524</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>31.953417164999998</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.496979094096523</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>3140.3575208953444</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>31.953417164999998</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>3149.213585471263</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$48,A11,'Species'!$U$2:$U$48))</x:f>
-        <x:v>100628.13543824863</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.496979094096523</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>3140.3575208953444</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>100345.15391241414</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>282.98152583448973</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.002820081636244</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.002820081636244128</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5991e44663cb4074"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re753e9499ade46b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5062,7 +4348,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -5161,7 +4447,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>178171427.7951421</x:v>
+        <x:v>175820957.12708527</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5175,7 +4461,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>178171427.7951421</x:v>
+        <x:v>177166073.02531397</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5189,7 +4475,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-2350470.6680568457</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5203,7 +4489,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-1005354.7698281407</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5214,9 +4500,9 @@
         <x:v>EEZ_219</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -5228,47 +4514,19 @@
         <x:v>EEZ_219</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_219</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_219</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ef646fd34d7459a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50a9ff48606445c8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5315,7 +4573,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
